--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/abr-2025.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/abr-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC abr-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC abr-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">

--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/abr-2025.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/abr-2025.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -575,7 +579,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2595-174-CM25</t>
+          <t>5482-61-SE25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,7 +594,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,17 +604,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.130.700-K</t>
+          <t>69.070.500-1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PARRAL</t>
+          <t>I MUNICIPALIDAD DE NUNOA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -623,20 +627,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>20382.58</v>
+        <v>232885.44</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>550716-5-CM25</t>
+          <t>2595-174-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -651,27 +659,27 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>65.961.370-0</t>
+          <t>69.130.700-K</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+          <t>I MUNICIPALIDAD DE PARRAL</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -684,20 +692,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>5722.4</v>
+        <v>20382.58</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1373053-3-CM25</t>
+          <t>550716-5-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -712,22 +724,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>65.961.370-0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -745,20 +757,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>7561.42</v>
+        <v>5722.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1373053-4-CM25</t>
+          <t>1373053-3-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -806,7 +822,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -819,7 +839,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>670784-4-CM25</t>
+          <t>1373053-4-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -834,7 +854,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +864,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE PENSIONES</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -867,20 +887,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>8556.65</v>
+        <v>7561.42</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2701-291-CM25</t>
+          <t>670784-4-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -905,12 +929,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -928,20 +952,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>6803.58</v>
+        <v>8556.65</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1186801-4-CM25</t>
+          <t>2701-291-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,22 +984,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>60.930.000-0</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE EDUCACION</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -989,74 +1017,147 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1076.18</v>
+        <v>6803.58</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>1186801-4-CM25</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>abr-2025</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025-04-24</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>60.930.000-0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>CONSEJO NACIONAL DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>1076.18</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>1477-153-CM25</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>2239-12-LR23</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>abr-2025</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>2025-04-29</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>70.786.200-9</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>BCI SEGUROS VIDA S A</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="M10" s="2" t="n">
+      <c r="M11" s="2" t="n">
         <v>30864.75</v>
       </c>
     </row>
